--- a/artfynd/A 57071-2024 artfynd.xlsx
+++ b/artfynd/A 57071-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111952009</v>
+        <v>111952005</v>
       </c>
       <c r="B2" t="n">
-        <v>89567</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546938</v>
+        <v>546821</v>
       </c>
       <c r="R2" t="n">
-        <v>7044594</v>
+        <v>7044588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,7 @@
         <v>111952008</v>
       </c>
       <c r="B3" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111952011</v>
+        <v>111952009</v>
       </c>
       <c r="B4" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546777</v>
+        <v>546938</v>
       </c>
       <c r="R4" t="n">
-        <v>7044566</v>
+        <v>7044594</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111952010</v>
+        <v>111951994</v>
       </c>
       <c r="B5" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547053</v>
+        <v>546681</v>
       </c>
       <c r="R5" t="n">
-        <v>7044643</v>
+        <v>7044541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111952005</v>
+        <v>111952011</v>
       </c>
       <c r="B6" t="n">
-        <v>89549</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546821</v>
+        <v>546777</v>
       </c>
       <c r="R6" t="n">
-        <v>7044587</v>
+        <v>7044566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1183,7 @@
         <v>111952012</v>
       </c>
       <c r="B7" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,12 +1284,7 @@
         <v>111952013</v>
       </c>
       <c r="B8" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,7 +1316,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>547009</v>
+        <v>547010</v>
       </c>
       <c r="R8" t="n">
         <v>7044708</v>

--- a/artfynd/A 57071-2024 artfynd.xlsx
+++ b/artfynd/A 57071-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952005</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952008</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952009</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111951994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952011</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,8 +1414,22 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111952013</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>